--- a/エラー画面.xlsx
+++ b/エラー画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e9caad2683a10f77/デスクトップ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3D6FD3F-178B-4D30-8A77-E5C86494AD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{919E33C3-80FC-4ED2-9AD9-1AF4829BB4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3B846589-D530-4917-9D49-BD1E8FA4EBE5}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AC281544-1AB9-4935-B13A-DDD11963036C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,21 +102,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>121228</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58C29D5C-1603-AD9E-F1B5-59591A9B9025}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DB3BEA8-CA8E-8945-3CFF-D20771B853AD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -126,13 +126,13 @@
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect l="60160" t="1923" r="30013" b="64579"/>
+        <a:srcRect l="65335" t="3126" r="6498" b="47076"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="346364"/>
-          <a:ext cx="4537364" cy="6033654"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12877800" cy="9105900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -141,336 +141,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D30070F6-404A-4E8E-22C4-85514BD462C8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:srcRect l="60429" t="1836" r="27522" b="62466"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5638800" y="381001"/>
-          <a:ext cx="5448300" cy="6610350"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>342901</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>190501</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>647701</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>228601</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F98B7D9F-6ED9-7674-A020-A70B67DF2BED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect l="60334" t="2500" r="8998" b="46036"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11908972" y="421822"/>
-          <a:ext cx="13911943" cy="9522279"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>619124</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="矢印: 右 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5E3ED8B-C65A-26E8-CF03-AC7316CA972D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4286250" y="2928937"/>
-          <a:ext cx="1166812" cy="1071563"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightArrow">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>642937</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>428624</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="矢印: 右 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F23B6D4-374F-2DAF-7A45-8230D6DDE84F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11001375" y="2933699"/>
-          <a:ext cx="1166812" cy="1066801"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightArrow">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>502782</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>40139</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="954107" cy="521425"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="テキスト ボックス 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0BA295A-0693-4460-FDC6-5E192342D8E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7986711" y="40139"/>
-          <a:ext cx="954107" cy="521425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>編集後</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>466723</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>40139</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="954107" cy="521425"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="テキスト ボックス 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88DEC6AB-104C-6243-9E47-9B760EFEBAFE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18156009" y="40139"/>
-          <a:ext cx="954107" cy="521425"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>送信後</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -770,7 +440,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E01E2DA8-238B-4C56-BB81-6650D6BCAB1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AADDE3E2-347D-4FB1-9F80-1DFDC228CDF7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
   <sheetData/>
